--- a/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/项目启动与治理-20260917-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/项目启动与治理-20260917-V1.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12660"/>
+    <workbookView windowWidth="28260" windowHeight="12720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="相关方管理" sheetId="1" r:id="rId1"/>
-    <sheet name="_数据接口" sheetId="2" r:id="rId2"/>
-    <sheet name="供应商POC计划" sheetId="3" r:id="rId3"/>
-    <sheet name="POC评分表" sheetId="4" r:id="rId4"/>
-    <sheet name="启动门禁清单" sheetId="5" r:id="rId5"/>
-    <sheet name="使用说明" sheetId="6" r:id="rId6"/>
+    <sheet name="供应商POC计划" sheetId="3" r:id="rId2"/>
+    <sheet name="POC评分表" sheetId="4" r:id="rId3"/>
+    <sheet name="启动门禁清单" sheetId="5" r:id="rId4"/>
+    <sheet name="使用说明" sheetId="6" r:id="rId5"/>
+    <sheet name="_数据接口" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -619,6 +619,696 @@
     <t>联系电话：18500001188</t>
   </si>
   <si>
+    <t>外部产品供应商POC计划</t>
+  </si>
+  <si>
+    <t>计划窗口：2026-08-15至2026-09-25。P0覆盖CA/电子签章、电子文档和BI报表；P1覆盖国产数据库和合同智能化预研。</t>
+  </si>
+  <si>
+    <t>候选供应商总数</t>
+  </si>
+  <si>
+    <t>P0候选数</t>
+  </si>
+  <si>
+    <t>P1候选数</t>
+  </si>
+  <si>
+    <t>待形成结论数</t>
+  </si>
+  <si>
+    <t>产品组</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>供应商/产品</t>
+  </si>
+  <si>
+    <t>联系人</t>
+  </si>
+  <si>
+    <t>联系电话</t>
+  </si>
+  <si>
+    <t>POC范围</t>
+  </si>
+  <si>
+    <t>评价维度</t>
+  </si>
+  <si>
+    <t>项目责任人</t>
+  </si>
+  <si>
+    <t>计划开始</t>
+  </si>
+  <si>
+    <t>计划结束</t>
+  </si>
+  <si>
+    <t>当前状态</t>
+  </si>
+  <si>
+    <t>必要输出</t>
+  </si>
+  <si>
+    <t>评审结论</t>
+  </si>
+  <si>
+    <t>电子文档</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>18500950569</t>
+  </si>
+  <si>
+    <t>验证在线编辑、版本协同、格式兼容、权限和归档集成</t>
+  </si>
+  <si>
+    <t>功能适配、格式兼容、权限安全、性能、集成复杂度</t>
+  </si>
+  <si>
+    <t>进行中（待确认）</t>
+  </si>
+  <si>
+    <t>POC报告、指标结果、问题清单、报价及服务承诺</t>
+  </si>
+  <si>
+    <t>结论由技术、业务、安全和采购联合评审</t>
+  </si>
+  <si>
+    <t>18201156495</t>
+  </si>
+  <si>
+    <t>18210225780</t>
+  </si>
+  <si>
+    <t>13520771314</t>
+  </si>
+  <si>
+    <t>BI报表</t>
+  </si>
+  <si>
+    <t>18519269076</t>
+  </si>
+  <si>
+    <t>验证合同统计分析、穿透查询、权限和大数据量报表能力</t>
+  </si>
+  <si>
+    <t>报表能力、权限隔离、性能、易用性、集成复杂度</t>
+  </si>
+  <si>
+    <t>15701252620</t>
+  </si>
+  <si>
+    <t>18810787659</t>
+  </si>
+  <si>
+    <t>CA/电子签章</t>
+  </si>
+  <si>
+    <t>18811229100</t>
+  </si>
+  <si>
+    <t>验证CA认证、签章流程、证据链、审计和合同归档</t>
+  </si>
+  <si>
+    <t>合规性、证据完整性、接口能力、性能、实施服务</t>
+  </si>
+  <si>
+    <t>13910655628</t>
+  </si>
+  <si>
+    <t>13701266895</t>
+  </si>
+  <si>
+    <t>15810436980</t>
+  </si>
+  <si>
+    <t>国产数据库</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>17610285971</t>
+  </si>
+  <si>
+    <t>验证兼容性、迁移工具、存储过程改造、性能与高可用</t>
+  </si>
+  <si>
+    <t>兼容性、迁移成本、性能、高可用、运维能力</t>
+  </si>
+  <si>
+    <t>18611668825</t>
+  </si>
+  <si>
+    <t>合同智能化</t>
+  </si>
+  <si>
+    <t>15210038699</t>
+  </si>
+  <si>
+    <t>验证条款识别、风险提示、知识库、准确率和可解释性</t>
+  </si>
+  <si>
+    <t>准确率、召回率、可解释性、数据安全、集成复杂度</t>
+  </si>
+  <si>
+    <t>15311254550</t>
+  </si>
+  <si>
+    <t>18600166523</t>
+  </si>
+  <si>
+    <t>18500001188</t>
+  </si>
+  <si>
+    <t>外部产品POC评分表</t>
+  </si>
+  <si>
+    <t>评分采用1—5分制。安全合规低于3分或任一维度低于2分时不通过；总分80分及以上通过，70—79分有条件通过。评分结果需联合评审确认。</t>
+  </si>
+  <si>
+    <t>候选供应商数</t>
+  </si>
+  <si>
+    <t>已完成评分数</t>
+  </si>
+  <si>
+    <t>通过/有条件通过</t>
+  </si>
+  <si>
+    <t>待评分数</t>
+  </si>
+  <si>
+    <t>权重</t>
+  </si>
+  <si>
+    <t>功能与业务适配</t>
+  </si>
+  <si>
+    <t>技术与集成</t>
+  </si>
+  <si>
+    <t>安全与合规</t>
+  </si>
+  <si>
+    <t>性能与稳定性</t>
+  </si>
+  <si>
+    <t>实施与服务</t>
+  </si>
+  <si>
+    <t>总拥有成本</t>
+  </si>
+  <si>
+    <t>加权总分</t>
+  </si>
+  <si>
+    <t>门槛结论</t>
+  </si>
+  <si>
+    <t>推荐结论</t>
+  </si>
+  <si>
+    <t>评审意见</t>
+  </si>
+  <si>
+    <t>证据链接/编号</t>
+  </si>
+  <si>
+    <t>项目启动准备门禁清单</t>
+  </si>
+  <si>
+    <t>评审窗口：2026-10-01至2026-10-16。必过项未通过时不得进入2026-10-20正式启动；有条件通过事项必须明确责任人和关闭日期。</t>
+  </si>
+  <si>
+    <t>门禁项总数</t>
+  </si>
+  <si>
+    <t>必过项</t>
+  </si>
+  <si>
+    <t>已通过</t>
+  </si>
+  <si>
+    <t>未关闭</t>
+  </si>
+  <si>
+    <t>门禁ID</t>
+  </si>
+  <si>
+    <t>领域</t>
+  </si>
+  <si>
+    <t>检查项</t>
+  </si>
+  <si>
+    <t>必要证据</t>
+  </si>
+  <si>
+    <t>负责人</t>
+  </si>
+  <si>
+    <t>配合人</t>
+  </si>
+  <si>
+    <t>计划完成</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>是否必过</t>
+  </si>
+  <si>
+    <t>未决问题/风险</t>
+  </si>
+  <si>
+    <t>纠偏行动</t>
+  </si>
+  <si>
+    <t>G01</t>
+  </si>
+  <si>
+    <t>治理</t>
+  </si>
+  <si>
+    <t>项目章程完成审批</t>
+  </si>
+  <si>
+    <t>批准版项目章程、授权与发起人确认</t>
+  </si>
+  <si>
+    <t>待确认</t>
+  </si>
+  <si>
+    <t>是</t>
+  </si>
+  <si>
+    <t>G02</t>
+  </si>
+  <si>
+    <t>价值</t>
+  </si>
+  <si>
+    <t>项目目标及价值指标确认</t>
+  </si>
+  <si>
+    <t>价值指标词典、基线、目标和收益责任人</t>
+  </si>
+  <si>
+    <t>业务负责人、产品经理</t>
+  </si>
+  <si>
+    <t>G03</t>
+  </si>
+  <si>
+    <t>范围</t>
+  </si>
+  <si>
+    <t>一期范围与排除项基线确认</t>
+  </si>
+  <si>
+    <t>范围说明书、WBS及需求分级原则</t>
+  </si>
+  <si>
+    <t>产品经理、技术经理</t>
+  </si>
+  <si>
+    <t>G04</t>
+  </si>
+  <si>
+    <t>进度</t>
+  </si>
+  <si>
+    <t>里程碑和主进度计划批准</t>
+  </si>
+  <si>
+    <t>里程碑计划、总控台账和关键路径检查</t>
+  </si>
+  <si>
+    <t>PMO</t>
+  </si>
+  <si>
+    <t>G05</t>
+  </si>
+  <si>
+    <t>成本</t>
+  </si>
+  <si>
+    <t>预算及成本控制口径确认</t>
+  </si>
+  <si>
+    <t>预算基线、人员单价、采购和预测口径</t>
+  </si>
+  <si>
+    <t>项目经理、财务/采购</t>
+  </si>
+  <si>
+    <t>G06</t>
+  </si>
+  <si>
+    <t>组织</t>
+  </si>
+  <si>
+    <t>治理组织与授权矩阵到位</t>
+  </si>
+  <si>
+    <t>指导委员会、CCB、业务专家组和授权矩阵</t>
+  </si>
+  <si>
+    <t>G07</t>
+  </si>
+  <si>
+    <t>相关方</t>
+  </si>
+  <si>
+    <t>相关方初评与沟通计划确认</t>
+  </si>
+  <si>
+    <t>相关方登记册、沟通计划和行动清单</t>
+  </si>
+  <si>
+    <t>G08</t>
+  </si>
+  <si>
+    <t>资源</t>
+  </si>
+  <si>
+    <t>30人团队及阶段资源计划确认</t>
+  </si>
+  <si>
+    <t>人员清单、到岗计划、周资源计划和关键技能备份</t>
+  </si>
+  <si>
+    <t>项目经理、各职能经理</t>
+  </si>
+  <si>
+    <t>G09</t>
+  </si>
+  <si>
+    <t>技术</t>
+  </si>
+  <si>
+    <t>总体技术架构基线通过</t>
+  </si>
+  <si>
+    <t>应用、数据、集成、安全和部署架构评审记录</t>
+  </si>
+  <si>
+    <t>高级开发、配置人员</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>外部产品</t>
+  </si>
+  <si>
+    <t>POC和选型建议完成</t>
+  </si>
+  <si>
+    <t>POC评分、问题清单、评审记录及选型建议</t>
+  </si>
+  <si>
+    <t>产品经理、测试、采购</t>
+  </si>
+  <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>需求</t>
+  </si>
+  <si>
+    <t>需求管理及基线计划就绪</t>
+  </si>
+  <si>
+    <t>调研计划、需求模板、优先级与追踪机制</t>
+  </si>
+  <si>
+    <t>业务代表、项目经理</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
+    <t>质量</t>
+  </si>
+  <si>
+    <t>质量计划和测试策略就绪</t>
+  </si>
+  <si>
+    <t>质量目标、测试分层、缺陷等级和门禁标准</t>
+  </si>
+  <si>
+    <t>测试负责人</t>
+  </si>
+  <si>
+    <t>技术经理、产品经理</t>
+  </si>
+  <si>
+    <t>G13</t>
+  </si>
+  <si>
+    <t>风险变更</t>
+  </si>
+  <si>
+    <t>风险、问题、变更和决策机制运行</t>
+  </si>
+  <si>
+    <t>台账、分级阈值、CCB流程及首次评审记录</t>
+  </si>
+  <si>
+    <t>PMO、各负责人</t>
+  </si>
+  <si>
+    <t>G14</t>
+  </si>
+  <si>
+    <t>采购合同</t>
+  </si>
+  <si>
+    <t>供应商与采购边界明确</t>
+  </si>
+  <si>
+    <t>采购计划、工作说明书、验收付款及退出条款</t>
+  </si>
+  <si>
+    <t>采购、法务、技术经理</t>
+  </si>
+  <si>
+    <t>G15</t>
+  </si>
+  <si>
+    <t>数据</t>
+  </si>
+  <si>
+    <t>数据治理和迁移策略确认</t>
+  </si>
+  <si>
+    <t>数据责任矩阵、质量规则、迁移及核对方案</t>
+  </si>
+  <si>
+    <t>技术经理、业务负责人</t>
+  </si>
+  <si>
+    <t>G16</t>
+  </si>
+  <si>
+    <t>安全合规</t>
+  </si>
+  <si>
+    <t>安全与合规要求纳入基线</t>
+  </si>
+  <si>
+    <t>分类分级、权限、审计、密码/信创与合规清单</t>
+  </si>
+  <si>
+    <t>安全、法务、配置人员</t>
+  </si>
+  <si>
+    <t>G17</t>
+  </si>
+  <si>
+    <t>环境配置</t>
+  </si>
+  <si>
+    <t>开发测试环境和配置机制就绪</t>
+  </si>
+  <si>
+    <t>环境清单、权限、代码库、流水线与配置审计</t>
+  </si>
+  <si>
+    <t>配置人员</t>
+  </si>
+  <si>
+    <t>技术经理、开发团队</t>
+  </si>
+  <si>
+    <t>G18</t>
+  </si>
+  <si>
+    <t>协作</t>
+  </si>
+  <si>
+    <t>会议、报告和升级机制发布</t>
+  </si>
+  <si>
+    <t>治理日历、周报模板、升级路径及联系人</t>
+  </si>
+  <si>
+    <t>G19</t>
+  </si>
+  <si>
+    <t>计划</t>
+  </si>
+  <si>
+    <t>项目整体管理计划获批</t>
+  </si>
+  <si>
+    <t>整体管理计划及各子计划会签记录</t>
+  </si>
+  <si>
+    <t>项目经理、各职能负责人</t>
+  </si>
+  <si>
+    <t>G20</t>
+  </si>
+  <si>
+    <t>启动决策</t>
+  </si>
+  <si>
+    <t>启动评审完成并形成正式决定</t>
+  </si>
+  <si>
+    <t>门禁检查表、遗留事项、批准/有条件批准记录</t>
+  </si>
+  <si>
+    <t>指导委员会</t>
+  </si>
+  <si>
+    <t>项目启动与治理-20260917-V1 使用说明</t>
+  </si>
+  <si>
+    <t>管理相关方、供应商POC、项目启动条件和治理决策。</t>
+  </si>
+  <si>
+    <t>项目</t>
+  </si>
+  <si>
+    <t>能源行业合同全生命周期管理系统</t>
+  </si>
+  <si>
+    <t>适用对象</t>
+  </si>
+  <si>
+    <t>项目集经理、项目经理、产品经理、技术经理</t>
+  </si>
+  <si>
+    <t>更新频率</t>
+  </si>
+  <si>
+    <t>相关方或POC状态变化时更新；启动门禁至少每周检查。</t>
+  </si>
+  <si>
+    <t>版本日期</t>
+  </si>
+  <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
+    <t>颜色约定</t>
+  </si>
+  <si>
+    <t>浅蓝表头；黄色为人工输入区；白色/灰色通常为公式、说明或系统数据。</t>
+  </si>
+  <si>
+    <t>推荐使用流程</t>
+  </si>
+  <si>
+    <t>维护相关方信息和沟通策略</t>
+  </si>
+  <si>
+    <t>登记外部产品POC计划</t>
+  </si>
+  <si>
+    <t>完成POC评分和选型结论</t>
+  </si>
+  <si>
+    <t>核对启动门禁及证据</t>
+  </si>
+  <si>
+    <t>将关键阻塞升级至PMO</t>
+  </si>
+  <si>
+    <t>工作表导航</t>
+  </si>
+  <si>
+    <t>顺序</t>
+  </si>
+  <si>
+    <t>工作表</t>
+  </si>
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>相关方管理</t>
+  </si>
+  <si>
+    <t>维护权力、关注度、参与度和沟通策略。</t>
+  </si>
+  <si>
+    <t>_数据接口</t>
+  </si>
+  <si>
+    <t>供Python脚本和AI PMO读取，人工一般不直接修改。</t>
+  </si>
+  <si>
+    <t>供应商POC计划</t>
+  </si>
+  <si>
+    <t>规划CA、电子文档、BI等外部产品验证。</t>
+  </si>
+  <si>
+    <t>POC评分表</t>
+  </si>
+  <si>
+    <t>记录POC评分、证据和选型意见。</t>
+  </si>
+  <si>
+    <t>启动门禁清单</t>
+  </si>
+  <si>
+    <t>核对正式启动前必须满足的条件。</t>
+  </si>
+  <si>
+    <t>维护与检查规则</t>
+  </si>
+  <si>
+    <t>先维护唯一编号、责任人、计划日期和状态，再补充说明与证据。</t>
+  </si>
+  <si>
+    <t>状态变化时同步更新实际日期、完成比例、阻塞原因或验证结果。</t>
+  </si>
+  <si>
+    <t>涉及基线、预算、范围、合同或上线门禁的变化，须先履行评审或审批。</t>
+  </si>
+  <si>
+    <t>不要覆盖公式、汇总区、图表数据区和“_数据接口”中的系统字段。</t>
+  </si>
+  <si>
+    <t>每周检查空责任人、逾期未完成、状态与日期矛盾、缺少证据和公式错误。</t>
+  </si>
+  <si>
+    <t>文件升级后，将被替换版本移入本模块_archive目录，不在正式目录保留多个现行版本。</t>
+  </si>
+  <si>
     <t>字段</t>
   </si>
   <si>
@@ -634,9 +1324,6 @@
     <t>项目名称</t>
   </si>
   <si>
-    <t>能源行业合同全生命周期管理系统</t>
-  </si>
-  <si>
     <t>模块编码</t>
   </si>
   <si>
@@ -653,693 +1340,6 @@
   </si>
   <si>
     <t>../90_项目数据中心/ai_pmo.db</t>
-  </si>
-  <si>
-    <t>外部产品供应商POC计划</t>
-  </si>
-  <si>
-    <t>计划窗口：2026-08-15至2026-09-25。P0覆盖CA/电子签章、电子文档和BI报表；P1覆盖国产数据库和合同智能化预研。</t>
-  </si>
-  <si>
-    <t>候选供应商总数</t>
-  </si>
-  <si>
-    <t>P0候选数</t>
-  </si>
-  <si>
-    <t>P1候选数</t>
-  </si>
-  <si>
-    <t>待形成结论数</t>
-  </si>
-  <si>
-    <t>产品组</t>
-  </si>
-  <si>
-    <t>优先级</t>
-  </si>
-  <si>
-    <t>供应商/产品</t>
-  </si>
-  <si>
-    <t>联系人</t>
-  </si>
-  <si>
-    <t>联系电话</t>
-  </si>
-  <si>
-    <t>POC范围</t>
-  </si>
-  <si>
-    <t>评价维度</t>
-  </si>
-  <si>
-    <t>项目责任人</t>
-  </si>
-  <si>
-    <t>计划开始</t>
-  </si>
-  <si>
-    <t>计划结束</t>
-  </si>
-  <si>
-    <t>当前状态</t>
-  </si>
-  <si>
-    <t>必要输出</t>
-  </si>
-  <si>
-    <t>评审结论</t>
-  </si>
-  <si>
-    <t>电子文档</t>
-  </si>
-  <si>
-    <t>P0</t>
-  </si>
-  <si>
-    <t>18500950569</t>
-  </si>
-  <si>
-    <t>验证在线编辑、版本协同、格式兼容、权限和归档集成</t>
-  </si>
-  <si>
-    <t>功能适配、格式兼容、权限安全、性能、集成复杂度</t>
-  </si>
-  <si>
-    <t>进行中（待确认）</t>
-  </si>
-  <si>
-    <t>POC报告、指标结果、问题清单、报价及服务承诺</t>
-  </si>
-  <si>
-    <t>结论由技术、业务、安全和采购联合评审</t>
-  </si>
-  <si>
-    <t>18201156495</t>
-  </si>
-  <si>
-    <t>18210225780</t>
-  </si>
-  <si>
-    <t>13520771314</t>
-  </si>
-  <si>
-    <t>BI报表</t>
-  </si>
-  <si>
-    <t>18519269076</t>
-  </si>
-  <si>
-    <t>验证合同统计分析、穿透查询、权限和大数据量报表能力</t>
-  </si>
-  <si>
-    <t>报表能力、权限隔离、性能、易用性、集成复杂度</t>
-  </si>
-  <si>
-    <t>15701252620</t>
-  </si>
-  <si>
-    <t>18810787659</t>
-  </si>
-  <si>
-    <t>CA/电子签章</t>
-  </si>
-  <si>
-    <t>18811229100</t>
-  </si>
-  <si>
-    <t>验证CA认证、签章流程、证据链、审计和合同归档</t>
-  </si>
-  <si>
-    <t>合规性、证据完整性、接口能力、性能、实施服务</t>
-  </si>
-  <si>
-    <t>13910655628</t>
-  </si>
-  <si>
-    <t>13701266895</t>
-  </si>
-  <si>
-    <t>15810436980</t>
-  </si>
-  <si>
-    <t>国产数据库</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>17610285971</t>
-  </si>
-  <si>
-    <t>验证兼容性、迁移工具、存储过程改造、性能与高可用</t>
-  </si>
-  <si>
-    <t>兼容性、迁移成本、性能、高可用、运维能力</t>
-  </si>
-  <si>
-    <t>18611668825</t>
-  </si>
-  <si>
-    <t>合同智能化</t>
-  </si>
-  <si>
-    <t>15210038699</t>
-  </si>
-  <si>
-    <t>验证条款识别、风险提示、知识库、准确率和可解释性</t>
-  </si>
-  <si>
-    <t>准确率、召回率、可解释性、数据安全、集成复杂度</t>
-  </si>
-  <si>
-    <t>15311254550</t>
-  </si>
-  <si>
-    <t>18600166523</t>
-  </si>
-  <si>
-    <t>18500001188</t>
-  </si>
-  <si>
-    <t>外部产品POC评分表</t>
-  </si>
-  <si>
-    <t>评分采用1—5分制。安全合规低于3分或任一维度低于2分时不通过；总分80分及以上通过，70—79分有条件通过。评分结果需联合评审确认。</t>
-  </si>
-  <si>
-    <t>候选供应商数</t>
-  </si>
-  <si>
-    <t>已完成评分数</t>
-  </si>
-  <si>
-    <t>通过/有条件通过</t>
-  </si>
-  <si>
-    <t>待评分数</t>
-  </si>
-  <si>
-    <t>权重</t>
-  </si>
-  <si>
-    <t>功能与业务适配</t>
-  </si>
-  <si>
-    <t>技术与集成</t>
-  </si>
-  <si>
-    <t>安全与合规</t>
-  </si>
-  <si>
-    <t>性能与稳定性</t>
-  </si>
-  <si>
-    <t>实施与服务</t>
-  </si>
-  <si>
-    <t>总拥有成本</t>
-  </si>
-  <si>
-    <t>加权总分</t>
-  </si>
-  <si>
-    <t>门槛结论</t>
-  </si>
-  <si>
-    <t>推荐结论</t>
-  </si>
-  <si>
-    <t>评审意见</t>
-  </si>
-  <si>
-    <t>证据链接/编号</t>
-  </si>
-  <si>
-    <t>项目启动准备门禁清单</t>
-  </si>
-  <si>
-    <t>评审窗口：2026-10-01至2026-10-16。必过项未通过时不得进入2026-10-20正式启动；有条件通过事项必须明确责任人和关闭日期。</t>
-  </si>
-  <si>
-    <t>门禁项总数</t>
-  </si>
-  <si>
-    <t>必过项</t>
-  </si>
-  <si>
-    <t>已通过</t>
-  </si>
-  <si>
-    <t>未关闭</t>
-  </si>
-  <si>
-    <t>门禁ID</t>
-  </si>
-  <si>
-    <t>领域</t>
-  </si>
-  <si>
-    <t>检查项</t>
-  </si>
-  <si>
-    <t>必要证据</t>
-  </si>
-  <si>
-    <t>负责人</t>
-  </si>
-  <si>
-    <t>配合人</t>
-  </si>
-  <si>
-    <t>计划完成</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>是否必过</t>
-  </si>
-  <si>
-    <t>未决问题/风险</t>
-  </si>
-  <si>
-    <t>纠偏行动</t>
-  </si>
-  <si>
-    <t>G01</t>
-  </si>
-  <si>
-    <t>治理</t>
-  </si>
-  <si>
-    <t>项目章程完成审批</t>
-  </si>
-  <si>
-    <t>批准版项目章程、授权与发起人确认</t>
-  </si>
-  <si>
-    <t>待确认</t>
-  </si>
-  <si>
-    <t>是</t>
-  </si>
-  <si>
-    <t>G02</t>
-  </si>
-  <si>
-    <t>价值</t>
-  </si>
-  <si>
-    <t>项目目标及价值指标确认</t>
-  </si>
-  <si>
-    <t>价值指标词典、基线、目标和收益责任人</t>
-  </si>
-  <si>
-    <t>业务负责人、产品经理</t>
-  </si>
-  <si>
-    <t>G03</t>
-  </si>
-  <si>
-    <t>范围</t>
-  </si>
-  <si>
-    <t>一期范围与排除项基线确认</t>
-  </si>
-  <si>
-    <t>范围说明书、WBS及需求分级原则</t>
-  </si>
-  <si>
-    <t>产品经理、技术经理</t>
-  </si>
-  <si>
-    <t>G04</t>
-  </si>
-  <si>
-    <t>进度</t>
-  </si>
-  <si>
-    <t>里程碑和主进度计划批准</t>
-  </si>
-  <si>
-    <t>里程碑计划、总控台账和关键路径检查</t>
-  </si>
-  <si>
-    <t>PMO</t>
-  </si>
-  <si>
-    <t>G05</t>
-  </si>
-  <si>
-    <t>成本</t>
-  </si>
-  <si>
-    <t>预算及成本控制口径确认</t>
-  </si>
-  <si>
-    <t>预算基线、人员单价、采购和预测口径</t>
-  </si>
-  <si>
-    <t>项目经理、财务/采购</t>
-  </si>
-  <si>
-    <t>G06</t>
-  </si>
-  <si>
-    <t>组织</t>
-  </si>
-  <si>
-    <t>治理组织与授权矩阵到位</t>
-  </si>
-  <si>
-    <t>指导委员会、CCB、业务专家组和授权矩阵</t>
-  </si>
-  <si>
-    <t>G07</t>
-  </si>
-  <si>
-    <t>相关方</t>
-  </si>
-  <si>
-    <t>相关方初评与沟通计划确认</t>
-  </si>
-  <si>
-    <t>相关方登记册、沟通计划和行动清单</t>
-  </si>
-  <si>
-    <t>G08</t>
-  </si>
-  <si>
-    <t>资源</t>
-  </si>
-  <si>
-    <t>30人团队及阶段资源计划确认</t>
-  </si>
-  <si>
-    <t>人员清单、到岗计划、周资源计划和关键技能备份</t>
-  </si>
-  <si>
-    <t>项目经理、各职能经理</t>
-  </si>
-  <si>
-    <t>G09</t>
-  </si>
-  <si>
-    <t>技术</t>
-  </si>
-  <si>
-    <t>总体技术架构基线通过</t>
-  </si>
-  <si>
-    <t>应用、数据、集成、安全和部署架构评审记录</t>
-  </si>
-  <si>
-    <t>高级开发、配置人员</t>
-  </si>
-  <si>
-    <t>G10</t>
-  </si>
-  <si>
-    <t>外部产品</t>
-  </si>
-  <si>
-    <t>POC和选型建议完成</t>
-  </si>
-  <si>
-    <t>POC评分、问题清单、评审记录及选型建议</t>
-  </si>
-  <si>
-    <t>产品经理、测试、采购</t>
-  </si>
-  <si>
-    <t>G11</t>
-  </si>
-  <si>
-    <t>需求</t>
-  </si>
-  <si>
-    <t>需求管理及基线计划就绪</t>
-  </si>
-  <si>
-    <t>调研计划、需求模板、优先级与追踪机制</t>
-  </si>
-  <si>
-    <t>业务代表、项目经理</t>
-  </si>
-  <si>
-    <t>G12</t>
-  </si>
-  <si>
-    <t>质量</t>
-  </si>
-  <si>
-    <t>质量计划和测试策略就绪</t>
-  </si>
-  <si>
-    <t>质量目标、测试分层、缺陷等级和门禁标准</t>
-  </si>
-  <si>
-    <t>测试负责人</t>
-  </si>
-  <si>
-    <t>技术经理、产品经理</t>
-  </si>
-  <si>
-    <t>G13</t>
-  </si>
-  <si>
-    <t>风险变更</t>
-  </si>
-  <si>
-    <t>风险、问题、变更和决策机制运行</t>
-  </si>
-  <si>
-    <t>台账、分级阈值、CCB流程及首次评审记录</t>
-  </si>
-  <si>
-    <t>PMO、各负责人</t>
-  </si>
-  <si>
-    <t>G14</t>
-  </si>
-  <si>
-    <t>采购合同</t>
-  </si>
-  <si>
-    <t>供应商与采购边界明确</t>
-  </si>
-  <si>
-    <t>采购计划、工作说明书、验收付款及退出条款</t>
-  </si>
-  <si>
-    <t>采购、法务、技术经理</t>
-  </si>
-  <si>
-    <t>G15</t>
-  </si>
-  <si>
-    <t>数据</t>
-  </si>
-  <si>
-    <t>数据治理和迁移策略确认</t>
-  </si>
-  <si>
-    <t>数据责任矩阵、质量规则、迁移及核对方案</t>
-  </si>
-  <si>
-    <t>技术经理、业务负责人</t>
-  </si>
-  <si>
-    <t>G16</t>
-  </si>
-  <si>
-    <t>安全合规</t>
-  </si>
-  <si>
-    <t>安全与合规要求纳入基线</t>
-  </si>
-  <si>
-    <t>分类分级、权限、审计、密码/信创与合规清单</t>
-  </si>
-  <si>
-    <t>安全、法务、配置人员</t>
-  </si>
-  <si>
-    <t>G17</t>
-  </si>
-  <si>
-    <t>环境配置</t>
-  </si>
-  <si>
-    <t>开发测试环境和配置机制就绪</t>
-  </si>
-  <si>
-    <t>环境清单、权限、代码库、流水线与配置审计</t>
-  </si>
-  <si>
-    <t>配置人员</t>
-  </si>
-  <si>
-    <t>技术经理、开发团队</t>
-  </si>
-  <si>
-    <t>G18</t>
-  </si>
-  <si>
-    <t>协作</t>
-  </si>
-  <si>
-    <t>会议、报告和升级机制发布</t>
-  </si>
-  <si>
-    <t>治理日历、周报模板、升级路径及联系人</t>
-  </si>
-  <si>
-    <t>G19</t>
-  </si>
-  <si>
-    <t>计划</t>
-  </si>
-  <si>
-    <t>项目整体管理计划获批</t>
-  </si>
-  <si>
-    <t>整体管理计划及各子计划会签记录</t>
-  </si>
-  <si>
-    <t>项目经理、各职能负责人</t>
-  </si>
-  <si>
-    <t>G20</t>
-  </si>
-  <si>
-    <t>启动决策</t>
-  </si>
-  <si>
-    <t>启动评审完成并形成正式决定</t>
-  </si>
-  <si>
-    <t>门禁检查表、遗留事项、批准/有条件批准记录</t>
-  </si>
-  <si>
-    <t>指导委员会</t>
-  </si>
-  <si>
-    <t>项目启动与治理-20260917-V1 使用说明</t>
-  </si>
-  <si>
-    <t>管理相关方、供应商POC、项目启动条件和治理决策。</t>
-  </si>
-  <si>
-    <t>项目</t>
-  </si>
-  <si>
-    <t>适用对象</t>
-  </si>
-  <si>
-    <t>项目集经理、项目经理、产品经理、技术经理</t>
-  </si>
-  <si>
-    <t>更新频率</t>
-  </si>
-  <si>
-    <t>相关方或POC状态变化时更新；启动门禁至少每周检查。</t>
-  </si>
-  <si>
-    <t>版本日期</t>
-  </si>
-  <si>
-    <t>2026-09-17</t>
-  </si>
-  <si>
-    <t>颜色约定</t>
-  </si>
-  <si>
-    <t>浅蓝表头；黄色为人工输入区；白色/灰色通常为公式、说明或系统数据。</t>
-  </si>
-  <si>
-    <t>推荐使用流程</t>
-  </si>
-  <si>
-    <t>维护相关方信息和沟通策略</t>
-  </si>
-  <si>
-    <t>登记外部产品POC计划</t>
-  </si>
-  <si>
-    <t>完成POC评分和选型结论</t>
-  </si>
-  <si>
-    <t>核对启动门禁及证据</t>
-  </si>
-  <si>
-    <t>将关键阻塞升级至PMO</t>
-  </si>
-  <si>
-    <t>工作表导航</t>
-  </si>
-  <si>
-    <t>顺序</t>
-  </si>
-  <si>
-    <t>工作表</t>
-  </si>
-  <si>
-    <t>用途</t>
-  </si>
-  <si>
-    <t>相关方管理</t>
-  </si>
-  <si>
-    <t>维护权力、关注度、参与度和沟通策略。</t>
-  </si>
-  <si>
-    <t>_数据接口</t>
-  </si>
-  <si>
-    <t>供Python脚本和AI PMO读取，人工一般不直接修改。</t>
-  </si>
-  <si>
-    <t>供应商POC计划</t>
-  </si>
-  <si>
-    <t>规划CA、电子文档、BI等外部产品验证。</t>
-  </si>
-  <si>
-    <t>POC评分表</t>
-  </si>
-  <si>
-    <t>记录POC评分、证据和选型意见。</t>
-  </si>
-  <si>
-    <t>启动门禁清单</t>
-  </si>
-  <si>
-    <t>核对正式启动前必须满足的条件。</t>
-  </si>
-  <si>
-    <t>维护与检查规则</t>
-  </si>
-  <si>
-    <t>先维护唯一编号、责任人、计划日期和状态，再补充说明与证据。</t>
-  </si>
-  <si>
-    <t>状态变化时同步更新实际日期、完成比例、阻塞原因或验证结果。</t>
-  </si>
-  <si>
-    <t>涉及基线、预算、范围、合同或上线门禁的变化，须先履行评审或审批。</t>
-  </si>
-  <si>
-    <t>不要覆盖公式、汇总区、图表数据区和“_数据接口”中的系统字段。</t>
-  </si>
-  <si>
-    <t>每周检查空责任人、逾期未完成、状态与日期矛盾、缺少证据和公式错误。</t>
-  </si>
-  <si>
-    <t>文件升级后，将被替换版本移入本模块_archive目录，不在正式目录保留多个现行版本。</t>
   </si>
 </sst>
 </file>
@@ -2958,7 +2958,7 @@
       <c r="O5" s="26"/>
       <c r="P5" s="27">
         <f ca="1">COUNTIFS($B$9:$B$108,"&lt;&gt;",$T$9:$T$108,"&lt;"&amp;TODAY(),$T$9:$T$108,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Q5" s="25"/>
       <c r="R5" s="26"/>
@@ -3152,7 +3152,7 @@
       <c r="AA9" s="31"/>
       <c r="AB9" s="32" t="str">
         <f ca="1" t="shared" ref="AB9:AB72" si="3">IF(B9="","",IF(AND(H9="高",OR(J9="抵触",J9="不支持")),"高权力不支持；","")&amp;IF(L9&gt;0,"存在支持差距；","")&amp;IF(AND(T9&lt;&gt;"",T9&lt;TODAY()),"沟通逾期；","")&amp;IF(AND(V9&lt;&gt;"",X9&lt;TODAY(),Y9&lt;&gt;"已完成"),"行动逾期；","")&amp;IF(AND(Z9="是",AA9=""),"未填升级对象",""))</f>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC9" s="31" t="s">
         <v>57</v>
@@ -3241,7 +3241,7 @@
       <c r="AA10" s="31"/>
       <c r="AB10" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC10" s="31" t="s">
         <v>57</v>
@@ -3330,7 +3330,7 @@
       <c r="AA11" s="31"/>
       <c r="AB11" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC11" s="31" t="s">
         <v>57</v>
@@ -3419,7 +3419,7 @@
       <c r="AA12" s="31"/>
       <c r="AB12" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC12" s="31" t="s">
         <v>57</v>
@@ -3508,7 +3508,7 @@
       <c r="AA13" s="31"/>
       <c r="AB13" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC13" s="31" t="s">
         <v>57</v>
@@ -3597,7 +3597,7 @@
       <c r="AA14" s="31"/>
       <c r="AB14" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC14" s="31" t="s">
         <v>57</v>
@@ -3686,7 +3686,7 @@
       <c r="AA15" s="31"/>
       <c r="AB15" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC15" s="31" t="s">
         <v>57</v>
@@ -3775,7 +3775,7 @@
       <c r="AA16" s="31"/>
       <c r="AB16" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC16" s="31" t="s">
         <v>57</v>
@@ -3864,7 +3864,7 @@
       <c r="AA17" s="31"/>
       <c r="AB17" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC17" s="31" t="s">
         <v>57</v>
@@ -3953,7 +3953,7 @@
       <c r="AA18" s="31"/>
       <c r="AB18" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC18" s="31" t="s">
         <v>57</v>
@@ -4042,7 +4042,7 @@
       <c r="AA19" s="31"/>
       <c r="AB19" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC19" s="31" t="s">
         <v>57</v>
@@ -4131,7 +4131,7 @@
       <c r="AA20" s="31"/>
       <c r="AB20" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC20" s="31" t="s">
         <v>57</v>
@@ -4220,7 +4220,7 @@
       <c r="AA21" s="31"/>
       <c r="AB21" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC21" s="31" t="s">
         <v>57</v>
@@ -4309,7 +4309,7 @@
       <c r="AA22" s="31"/>
       <c r="AB22" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC22" s="31" t="s">
         <v>57</v>
@@ -4398,7 +4398,7 @@
       <c r="AA23" s="31"/>
       <c r="AB23" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC23" s="31" t="s">
         <v>106</v>
@@ -4487,7 +4487,7 @@
       <c r="AA24" s="31"/>
       <c r="AB24" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC24" s="31" t="s">
         <v>110</v>
@@ -4576,7 +4576,7 @@
       <c r="AA25" s="31"/>
       <c r="AB25" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC25" s="31" t="s">
         <v>114</v>
@@ -4665,7 +4665,7 @@
       <c r="AA26" s="31"/>
       <c r="AB26" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC26" s="31" t="s">
         <v>124</v>
@@ -4754,7 +4754,7 @@
       <c r="AA27" s="31"/>
       <c r="AB27" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC27" s="31" t="s">
         <v>128</v>
@@ -4843,7 +4843,7 @@
       <c r="AA28" s="31"/>
       <c r="AB28" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC28" s="31" t="s">
         <v>132</v>
@@ -4932,7 +4932,7 @@
       <c r="AA29" s="31"/>
       <c r="AB29" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC29" s="31" t="s">
         <v>136</v>
@@ -5021,7 +5021,7 @@
       <c r="AA30" s="31"/>
       <c r="AB30" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC30" s="31" t="s">
         <v>141</v>
@@ -5110,7 +5110,7 @@
       <c r="AA31" s="31"/>
       <c r="AB31" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC31" s="31" t="s">
         <v>145</v>
@@ -5199,7 +5199,7 @@
       <c r="AA32" s="31"/>
       <c r="AB32" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC32" s="31" t="s">
         <v>149</v>
@@ -5288,7 +5288,7 @@
       <c r="AA33" s="31"/>
       <c r="AB33" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC33" s="31" t="s">
         <v>155</v>
@@ -5377,7 +5377,7 @@
       <c r="AA34" s="31"/>
       <c r="AB34" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC34" s="31" t="s">
         <v>159</v>
@@ -5466,7 +5466,7 @@
       <c r="AA35" s="31"/>
       <c r="AB35" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC35" s="31" t="s">
         <v>163</v>
@@ -5555,7 +5555,7 @@
       <c r="AA36" s="31"/>
       <c r="AB36" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC36" s="31" t="s">
         <v>168</v>
@@ -5644,7 +5644,7 @@
       <c r="AA37" s="31"/>
       <c r="AB37" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC37" s="31" t="s">
         <v>173</v>
@@ -5733,7 +5733,7 @@
       <c r="AA38" s="31"/>
       <c r="AB38" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC38" s="31" t="s">
         <v>177</v>
@@ -5822,7 +5822,7 @@
       <c r="AA39" s="31"/>
       <c r="AB39" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC39" s="31" t="s">
         <v>182</v>
@@ -5911,7 +5911,7 @@
       <c r="AA40" s="31"/>
       <c r="AB40" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC40" s="31" t="s">
         <v>186</v>
@@ -6000,7 +6000,7 @@
       <c r="AA41" s="31"/>
       <c r="AB41" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC41" s="31" t="s">
         <v>190</v>
@@ -6089,7 +6089,7 @@
       <c r="AA42" s="31"/>
       <c r="AB42" s="32" t="str">
         <f ca="1" t="shared" si="3"/>
-        <v>存在支持差距；</v>
+        <v>存在支持差距；沟通逾期；</v>
       </c>
       <c r="AC42" s="31" t="s">
         <v>194</v>
@@ -8987,66 +8987,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="1"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B1" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B6" t="s">
-        <v>206</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
@@ -9069,7 +9009,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:14">
       <c r="A1" s="11" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -9087,7 +9027,7 @@
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:14">
       <c r="A2" s="12" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -9121,22 +9061,22 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="13" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
       <c r="J4" s="13" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="K4" s="13"/>
       <c r="L4" s="21"/>
@@ -9189,43 +9129,43 @@
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:14">
       <c r="A7" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="M7" s="15" t="s">
         <v>213</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="H7" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="I7" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="J7" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="K7" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="L7" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>225</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>39</v>
@@ -9233,10 +9173,10 @@
     </row>
     <row r="8" ht="38" customHeight="1" spans="1:14">
       <c r="A8" s="16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>116</v>
@@ -9245,13 +9185,13 @@
         <v>115</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="H8" s="16" t="s">
         <v>84</v>
@@ -9263,24 +9203,24 @@
         <v>46290</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L8" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M8" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9" ht="38" customHeight="1" spans="1:14">
       <c r="A9" s="16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>126</v>
@@ -9289,13 +9229,13 @@
         <v>125</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>84</v>
@@ -9307,24 +9247,24 @@
         <v>46290</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L9" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M9" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" ht="38" customHeight="1" spans="1:14">
       <c r="A10" s="16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>130</v>
@@ -9333,13 +9273,13 @@
         <v>129</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="H10" s="16" t="s">
         <v>84</v>
@@ -9351,24 +9291,24 @@
         <v>46290</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L10" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M10" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" ht="38" customHeight="1" spans="1:14">
       <c r="A11" s="16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>134</v>
@@ -9377,13 +9317,13 @@
         <v>133</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="H11" s="16" t="s">
         <v>84</v>
@@ -9395,24 +9335,24 @@
         <v>46290</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L11" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M11" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" ht="38" customHeight="1" spans="1:14">
       <c r="A12" s="16" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>138</v>
@@ -9421,13 +9361,13 @@
         <v>137</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="H12" s="16" t="s">
         <v>84</v>
@@ -9439,24 +9379,24 @@
         <v>46290</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M12" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" ht="38" customHeight="1" spans="1:14">
       <c r="A13" s="16" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>143</v>
@@ -9465,13 +9405,13 @@
         <v>142</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="H13" s="16" t="s">
         <v>84</v>
@@ -9483,24 +9423,24 @@
         <v>46290</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L13" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M13" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" ht="38" customHeight="1" spans="1:14">
       <c r="A14" s="16" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>147</v>
@@ -9509,13 +9449,13 @@
         <v>146</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="H14" s="16" t="s">
         <v>84</v>
@@ -9527,24 +9467,24 @@
         <v>46290</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M14" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1" spans="1:14">
       <c r="A15" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>151</v>
@@ -9553,13 +9493,13 @@
         <v>150</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="H15" s="16" t="s">
         <v>154</v>
@@ -9571,24 +9511,24 @@
         <v>46290</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M15" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1" spans="1:14">
       <c r="A16" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>157</v>
@@ -9597,13 +9537,13 @@
         <v>156</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="H16" s="16" t="s">
         <v>154</v>
@@ -9615,24 +9555,24 @@
         <v>46290</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M16" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1" spans="1:14">
       <c r="A17" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>161</v>
@@ -9641,13 +9581,13 @@
         <v>160</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="H17" s="16" t="s">
         <v>154</v>
@@ -9659,24 +9599,24 @@
         <v>46290</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L17" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M17" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1" spans="1:14">
       <c r="A18" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>165</v>
@@ -9685,13 +9625,13 @@
         <v>164</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="F18" s="17" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="H18" s="16" t="s">
         <v>154</v>
@@ -9703,24 +9643,24 @@
         <v>46290</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M18" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1" spans="1:14">
       <c r="A19" s="16" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>170</v>
@@ -9729,13 +9669,13 @@
         <v>169</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="H19" s="16" t="s">
         <v>63</v>
@@ -9747,24 +9687,24 @@
         <v>46290</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L19" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M19" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1" spans="1:14">
       <c r="A20" s="16" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>175</v>
@@ -9773,13 +9713,13 @@
         <v>174</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="H20" s="16" t="s">
         <v>63</v>
@@ -9791,24 +9731,24 @@
         <v>46290</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M20" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1" spans="1:14">
       <c r="A21" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>179</v>
@@ -9817,13 +9757,13 @@
         <v>178</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="H21" s="16" t="s">
         <v>154</v>
@@ -9835,24 +9775,24 @@
         <v>46290</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L21" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M21" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1" spans="1:14">
       <c r="A22" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>184</v>
@@ -9861,13 +9801,13 @@
         <v>183</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="H22" s="16" t="s">
         <v>154</v>
@@ -9879,24 +9819,24 @@
         <v>46290</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L22" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M22" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="23" ht="38" customHeight="1" spans="1:14">
       <c r="A23" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>188</v>
@@ -9905,13 +9845,13 @@
         <v>187</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="H23" s="16" t="s">
         <v>154</v>
@@ -9923,24 +9863,24 @@
         <v>46290</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L23" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M23" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" ht="38" customHeight="1" spans="1:14">
       <c r="A24" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>192</v>
@@ -9949,13 +9889,13 @@
         <v>191</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="H24" s="16" t="s">
         <v>154</v>
@@ -9967,16 +9907,16 @@
         <v>46290</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L24" s="17" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="M24" s="17" t="s">
         <v>57</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -10011,7 +9951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
@@ -10034,29 +9974,29 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:15">
       <c r="A1" s="11" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:15">
       <c r="A2" s="12" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" s="13" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B4" s="13"/>
       <c r="D4" s="13" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="E4" s="13"/>
       <c r="G4" s="13" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="H4" s="13"/>
       <c r="J4" s="13" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="K4" s="13"/>
     </row>
@@ -10084,7 +10024,7 @@
     </row>
     <row r="6" spans="1:15">
       <c r="D6" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="E6" s="19">
         <v>0.25</v>
@@ -10107,57 +10047,57 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="15" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="N7" s="15" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="O7" s="15" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:15">
       <c r="A8" s="16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C8" s="16" t="s">
         <v>116</v>
@@ -10192,10 +10132,10 @@
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:15">
       <c r="A9" s="16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C9" s="16" t="s">
         <v>126</v>
@@ -10230,10 +10170,10 @@
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:15">
       <c r="A10" s="16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>130</v>
@@ -10268,10 +10208,10 @@
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:15">
       <c r="A11" s="16" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>134</v>
@@ -10306,10 +10246,10 @@
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:15">
       <c r="A12" s="16" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>138</v>
@@ -10344,10 +10284,10 @@
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:15">
       <c r="A13" s="16" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C13" s="16" t="s">
         <v>143</v>
@@ -10382,10 +10322,10 @@
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:15">
       <c r="A14" s="16" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>147</v>
@@ -10420,10 +10360,10 @@
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:15">
       <c r="A15" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C15" s="16" t="s">
         <v>151</v>
@@ -10458,10 +10398,10 @@
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:15">
       <c r="A16" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>157</v>
@@ -10496,10 +10436,10 @@
     </row>
     <row r="17" ht="30" customHeight="1" spans="1:15">
       <c r="A17" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C17" s="16" t="s">
         <v>161</v>
@@ -10534,10 +10474,10 @@
     </row>
     <row r="18" ht="30" customHeight="1" spans="1:15">
       <c r="A18" s="16" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="C18" s="16" t="s">
         <v>165</v>
@@ -10572,10 +10512,10 @@
     </row>
     <row r="19" ht="30" customHeight="1" spans="1:15">
       <c r="A19" s="16" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C19" s="16" t="s">
         <v>170</v>
@@ -10610,10 +10550,10 @@
     </row>
     <row r="20" ht="30" customHeight="1" spans="1:15">
       <c r="A20" s="16" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C20" s="16" t="s">
         <v>175</v>
@@ -10648,10 +10588,10 @@
     </row>
     <row r="21" ht="30" customHeight="1" spans="1:15">
       <c r="A21" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C21" s="16" t="s">
         <v>179</v>
@@ -10686,10 +10626,10 @@
     </row>
     <row r="22" ht="30" customHeight="1" spans="1:15">
       <c r="A22" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C22" s="16" t="s">
         <v>184</v>
@@ -10724,10 +10664,10 @@
     </row>
     <row r="23" ht="30" customHeight="1" spans="1:15">
       <c r="A23" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C23" s="16" t="s">
         <v>188</v>
@@ -10762,10 +10702,10 @@
     </row>
     <row r="24" ht="30" customHeight="1" spans="1:15">
       <c r="A24" s="16" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="C24" s="16" t="s">
         <v>192</v>
@@ -10837,7 +10777,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
@@ -10861,29 +10801,29 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:13">
       <c r="A1" s="11" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:13">
       <c r="A2" s="12" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="13" t="s">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B4" s="13"/>
       <c r="D4" s="13" t="s">
-        <v>284</v>
+        <v>272</v>
       </c>
       <c r="E4" s="13"/>
       <c r="G4" s="13" t="s">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="H4" s="13"/>
       <c r="J4" s="13" t="s">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="K4" s="13"/>
     </row>
@@ -10911,40 +10851,40 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="15" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="L7" s="15" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="M7" s="15" t="s">
         <v>39</v>
@@ -10952,16 +10892,16 @@
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:13">
       <c r="A8" s="16" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>103</v>
@@ -10973,10 +10913,10 @@
         <v>46300</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I8" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J8" s="16" t="s">
         <v>57</v>
@@ -10993,31 +10933,31 @@
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:13">
       <c r="A9" s="16" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="E9" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="G9" s="18">
         <v>46301</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>57</v>
@@ -11034,31 +10974,31 @@
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:13">
       <c r="A10" s="16" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>98</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="G10" s="18">
         <v>46302</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J10" s="16" t="s">
         <v>57</v>
@@ -11075,31 +11015,31 @@
     </row>
     <row r="11" ht="34" customHeight="1" spans="1:13">
       <c r="A11" s="16" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>98</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="G11" s="18">
         <v>46303</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>57</v>
@@ -11116,31 +11056,31 @@
     </row>
     <row r="12" ht="34" customHeight="1" spans="1:13">
       <c r="A12" s="16" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="G12" s="18">
         <v>46303</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>57</v>
@@ -11157,31 +11097,31 @@
     </row>
     <row r="13" ht="34" customHeight="1" spans="1:13">
       <c r="A13" s="16" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="E13" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="G13" s="18">
         <v>46304</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>57</v>
@@ -11198,28 +11138,28 @@
     </row>
     <row r="14" ht="34" customHeight="1" spans="1:13">
       <c r="A14" s="16" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="E14" s="16" t="s">
         <v>98</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="G14" s="18">
         <v>46304</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>56</v>
@@ -11239,31 +11179,31 @@
     </row>
     <row r="15" ht="34" customHeight="1" spans="1:13">
       <c r="A15" s="16" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="E15" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="G15" s="18">
         <v>46305</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>57</v>
@@ -11280,31 +11220,31 @@
     </row>
     <row r="16" ht="34" customHeight="1" spans="1:13">
       <c r="A16" s="16" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="E16" s="16" t="s">
         <v>107</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="G16" s="18">
         <v>46305</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>57</v>
@@ -11321,31 +11261,31 @@
     </row>
     <row r="17" ht="34" customHeight="1" spans="1:13">
       <c r="A17" s="16" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="E17" s="16" t="s">
         <v>107</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
       <c r="G17" s="18">
         <v>46290</v>
       </c>
       <c r="H17" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>57</v>
@@ -11362,31 +11302,31 @@
     </row>
     <row r="18" ht="34" customHeight="1" spans="1:13">
       <c r="A18" s="16" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="E18" s="16" t="s">
         <v>111</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="G18" s="18">
         <v>46306</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>57</v>
@@ -11403,31 +11343,31 @@
     </row>
     <row r="19" ht="34" customHeight="1" spans="1:13">
       <c r="A19" s="16" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="G19" s="18">
         <v>46306</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J19" s="16" t="s">
         <v>57</v>
@@ -11444,31 +11384,31 @@
     </row>
     <row r="20" ht="34" customHeight="1" spans="1:13">
       <c r="A20" s="16" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
       <c r="E20" s="16" t="s">
         <v>98</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="G20" s="18">
         <v>46307</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>57</v>
@@ -11485,28 +11425,28 @@
     </row>
     <row r="21" ht="34" customHeight="1" spans="1:13">
       <c r="A21" s="16" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="G21" s="18">
         <v>46307</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I21" s="16" t="s">
         <v>56</v>
@@ -11526,31 +11466,31 @@
     </row>
     <row r="22" ht="34" customHeight="1" spans="1:13">
       <c r="A22" s="16" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="E22" s="16" t="s">
         <v>111</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="G22" s="18">
         <v>46308</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J22" s="16" t="s">
         <v>57</v>
@@ -11567,31 +11507,31 @@
     </row>
     <row r="23" ht="34" customHeight="1" spans="1:13">
       <c r="A23" s="16" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E23" s="16" t="s">
         <v>107</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="G23" s="18">
         <v>46308</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J23" s="16" t="s">
         <v>57</v>
@@ -11608,31 +11548,31 @@
     </row>
     <row r="24" ht="34" customHeight="1" spans="1:13">
       <c r="A24" s="16" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="G24" s="18">
         <v>46309</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J24" s="16" t="s">
         <v>57</v>
@@ -11649,28 +11589,28 @@
     </row>
     <row r="25" ht="34" customHeight="1" spans="1:13">
       <c r="A25" s="16" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="E25" s="16" t="s">
         <v>98</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="G25" s="18">
         <v>46309</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I25" s="16" t="s">
         <v>56</v>
@@ -11690,31 +11630,31 @@
     </row>
     <row r="26" ht="34" customHeight="1" spans="1:13">
       <c r="A26" s="16" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="E26" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="G26" s="18">
         <v>46310</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J26" s="16" t="s">
         <v>57</v>
@@ -11731,31 +11671,31 @@
     </row>
     <row r="27" ht="34" customHeight="1" spans="1:13">
       <c r="A27" s="16" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>103</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="G27" s="18">
         <v>46311</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="J27" s="16" t="s">
         <v>57</v>
@@ -11802,7 +11742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <tabColor rgb="FF7F8C8D"/>
@@ -11818,7 +11758,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -11830,7 +11770,7 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:8">
       <c r="A2" s="2" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -11852,10 +11792,10 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:8">
       <c r="A4" s="4" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>200</v>
+        <v>389</v>
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="3"/>
@@ -11866,10 +11806,10 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:8">
       <c r="A5" s="4" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="3"/>
@@ -11880,10 +11820,10 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:8">
       <c r="A6" s="4" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" s="3"/>
@@ -11894,10 +11834,10 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="3"/>
@@ -11908,10 +11848,10 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:8">
       <c r="A8" s="4" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="3"/>
@@ -11932,7 +11872,7 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:8">
       <c r="A10" s="7" t="s">
-        <v>409</v>
+        <v>398</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -11947,7 +11887,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
@@ -11961,7 +11901,7 @@
         <v>2</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>411</v>
+        <v>400</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
@@ -11975,7 +11915,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>412</v>
+        <v>401</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
@@ -11989,7 +11929,7 @@
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>413</v>
+        <v>402</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -12003,7 +11943,7 @@
         <v>5</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>414</v>
+        <v>403</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
@@ -12034,7 +11974,7 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:8">
       <c r="A18" s="7" t="s">
-        <v>415</v>
+        <v>404</v>
       </c>
       <c r="B18" s="8"/>
       <c r="C18" s="8"/>
@@ -12046,13 +11986,13 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:8">
       <c r="A19" s="10" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>417</v>
+        <v>406</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>418</v>
+        <v>407</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -12065,10 +12005,10 @@
         <v>1</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>419</v>
+        <v>408</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>420</v>
+        <v>409</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -12081,10 +12021,10 @@
         <v>2</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>421</v>
+        <v>410</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>422</v>
+        <v>411</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -12097,10 +12037,10 @@
         <v>3</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -12113,10 +12053,10 @@
         <v>4</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>425</v>
+        <v>414</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>426</v>
+        <v>415</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -12129,10 +12069,10 @@
         <v>5</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -12152,7 +12092,7 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:8">
       <c r="A26" s="7" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -12167,7 +12107,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>430</v>
+        <v>419</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -12181,7 +12121,7 @@
         <v>2</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
@@ -12195,7 +12135,7 @@
         <v>3</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -12209,7 +12149,7 @@
         <v>4</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -12223,7 +12163,7 @@
         <v>5</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -12237,7 +12177,7 @@
         <v>6</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -12273,4 +12213,64 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="1"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B2" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B3" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>430</v>
+      </c>
+      <c r="B4" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>432</v>
+      </c>
+      <c r="B5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>434</v>
+      </c>
+      <c r="B6" t="s">
+        <v>435</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/项目启动与治理-20260917-V1.xlsx
+++ b/合同全生命周期管理系统-项目管理套件/01_项目启动与治理/项目启动与治理-20260917-V1.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28260" windowHeight="12720" activeTab="3"/>
+    <workbookView windowWidth="28260" windowHeight="12720" activeTab="0"/>
   </bookViews>
   <sheets>
+    <sheet name="使用说明" sheetId="6" r:id="rId5"/>
     <sheet name="相关方管理" sheetId="1" r:id="rId1"/>
     <sheet name="供应商POC计划" sheetId="3" r:id="rId2"/>
     <sheet name="POC评分表" sheetId="4" r:id="rId3"/>
     <sheet name="启动门禁清单" sheetId="5" r:id="rId4"/>
-    <sheet name="使用说明" sheetId="6" r:id="rId5"/>
     <sheet name="_数据接口" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
